--- a/integrated_dyes_data.xlsx
+++ b/integrated_dyes_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\C&amp;T Dye Finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AF43F5-97FB-4BBF-902A-87872C5FFAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7006173-AFE7-49C2-A4AC-ED1EACACDD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E355BAF3-81A5-4751-AE4F-EE2EF90875A4}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$34</definedName>
   </definedNames>
-  <calcPr calcId="181029" iterateCount="1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="72">
   <si>
     <t>염료그룹</t>
   </si>
@@ -246,6 +246,25 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>Sunfix SPD conc.</t>
+  </si>
+  <si>
+    <t>Novacron Yellow NP (Sunfron Yellow NP)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synozol Red HF-3B (Sunfix Red S2B)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Synozol Yellow K-3RS (Sunfix Yellow SPD conc)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rifafix Violet 5RN (Sunfix Violet S5R)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -759,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25ACC554-19B0-43F2-ABD1-883041E60297}">
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.875" style="3" bestFit="1" customWidth="1"/>
@@ -1168,10 +1187,10 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C7" s="9">
         <v>6.5</v>
@@ -1219,17 +1238,17 @@
         <v>0</v>
       </c>
       <c r="R7" s="6">
-        <v>45.3566</v>
+        <v>45.043399999999998</v>
       </c>
       <c r="S7" s="6">
-        <v>57.023699999999998</v>
+        <v>56.629899999999999</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="6">
-        <v>33.909999999999997</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="V7" s="6">
-        <v>83.477500000000006</v>
+        <v>84.53</v>
       </c>
       <c r="W7" s="6">
         <v>100</v>
@@ -1243,22 +1262,22 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="D8" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="E8" s="10">
-        <v>2.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F8" s="10">
         <v>4.5</v>
       </c>
-      <c r="G8" s="10">
-        <v>4.5</v>
+      <c r="G8" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>11</v>
@@ -1281,27 +1300,27 @@
       <c r="N8" s="13">
         <v>4.5</v>
       </c>
-      <c r="O8" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="P8" s="13">
-        <v>4.5</v>
+      <c r="O8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="Q8" s="4">
         <v>0</v>
       </c>
       <c r="R8" s="6">
-        <v>36.665900000000001</v>
+        <v>45.3566</v>
       </c>
       <c r="S8" s="6">
-        <v>46.097499999999997</v>
+        <v>57.023699999999998</v>
       </c>
       <c r="T8" s="6"/>
       <c r="U8" s="6">
-        <v>37.78</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="V8" s="6">
-        <v>84.444999999999993</v>
+        <v>83.477500000000006</v>
       </c>
       <c r="W8" s="6">
         <v>100</v>
@@ -1315,10 +1334,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>11</v>
+        <v>69</v>
+      </c>
+      <c r="C9" s="9">
+        <v>4.5</v>
       </c>
       <c r="D9" s="10">
         <v>3.5</v>
@@ -1326,17 +1345,17 @@
       <c r="E9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>11</v>
+      <c r="F9" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>4.5</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="10">
-        <v>3.5</v>
+      <c r="I9" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="J9" s="13">
         <v>4.5</v>
@@ -1350,8 +1369,8 @@
       <c r="M9" s="13">
         <v>4.5</v>
       </c>
-      <c r="N9" s="13" t="s">
-        <v>64</v>
+      <c r="N9" s="13">
+        <v>4.5</v>
       </c>
       <c r="O9" s="13" t="s">
         <v>64</v>
@@ -1363,17 +1382,17 @@
         <v>0</v>
       </c>
       <c r="R9" s="6">
-        <v>46</v>
+        <v>37.041899999999998</v>
       </c>
       <c r="S9" s="6">
-        <v>56</v>
+        <v>46.570099999999996</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="6">
-        <v>41.83</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="V9" s="6">
-        <v>85.457499999999996</v>
+        <v>84.53</v>
       </c>
       <c r="W9" s="6">
         <v>100</v>
@@ -1387,7 +1406,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="9">
         <v>4.5</v>
@@ -1395,8 +1414,8 @@
       <c r="D10" s="10">
         <v>3.5</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>12</v>
+      <c r="E10" s="10">
+        <v>2.5</v>
       </c>
       <c r="F10" s="10">
         <v>4.5</v>
@@ -1404,48 +1423,48 @@
       <c r="G10" s="10">
         <v>4.5</v>
       </c>
-      <c r="H10" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>11</v>
+      <c r="H10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="10">
+        <v>4.5</v>
       </c>
       <c r="J10" s="13">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K10" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>65</v>
+        <v>4.5</v>
+      </c>
+      <c r="L10" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M10" s="13">
+        <v>4.5</v>
       </c>
       <c r="N10" s="13">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O10" s="13">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P10" s="13">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q10" s="4">
         <v>0</v>
       </c>
       <c r="R10" s="6">
-        <v>25.194400000000002</v>
+        <v>36.665900000000001</v>
       </c>
       <c r="S10" s="6">
-        <v>31.6751</v>
+        <v>46.097499999999997</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="6">
-        <v>22.07</v>
+        <v>37.78</v>
       </c>
       <c r="V10" s="6">
-        <v>80.517499999999998</v>
+        <v>84.444999999999993</v>
       </c>
       <c r="W10" s="6">
         <v>100</v>
@@ -1459,19 +1478,19 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>11</v>
+      <c r="D11" s="10">
+        <v>3.5</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="10">
-        <v>4.5</v>
+      <c r="F11" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>11</v>
@@ -1479,8 +1498,8 @@
       <c r="H11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>11</v>
+      <c r="I11" s="10">
+        <v>3.5</v>
       </c>
       <c r="J11" s="13">
         <v>4.5</v>
@@ -1507,17 +1526,17 @@
         <v>0</v>
       </c>
       <c r="R11" s="6">
-        <v>50.2301</v>
+        <v>46</v>
       </c>
       <c r="S11" s="6">
-        <v>63.150799999999997</v>
+        <v>56</v>
       </c>
       <c r="T11" s="6"/>
       <c r="U11" s="6">
-        <v>49.16</v>
+        <v>41.83</v>
       </c>
       <c r="V11" s="6">
-        <v>87.29</v>
+        <v>85.457499999999996</v>
       </c>
       <c r="W11" s="6">
         <v>100</v>
@@ -1528,68 +1547,68 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="C12" s="9">
+        <v>4.5</v>
       </c>
       <c r="D12" s="10">
         <v>3.5</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G12" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="K12" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="13">
         <v>2.5</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="I12" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="J12" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="K12" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L12" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="M12" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N12" s="13">
-        <v>4.5</v>
-      </c>
       <c r="O12" s="13">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="P12" s="13">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" s="4">
         <v>0</v>
       </c>
       <c r="R12" s="6">
-        <v>44.933100000000003</v>
+        <v>25.194400000000002</v>
       </c>
       <c r="S12" s="6">
-        <v>56.491199999999999</v>
+        <v>31.6751</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6">
-        <v>84.7</v>
+        <v>22.07</v>
       </c>
       <c r="V12" s="6">
-        <v>96.174999999999997</v>
+        <v>80.517499999999998</v>
       </c>
       <c r="W12" s="6">
         <v>100</v>
@@ -1600,31 +1619,31 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="E13" s="10">
-        <v>3.5</v>
+        <v>11</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="F13" s="10">
         <v>4.5</v>
       </c>
-      <c r="G13" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="H13" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I13" s="10">
-        <v>4.5</v>
+      <c r="G13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="J13" s="13">
         <v>4.5</v>
@@ -1647,128 +1666,128 @@
       <c r="P13" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="Q13" s="7">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>25</v>
-      </c>
-      <c r="S13" s="8">
-        <v>54</v>
-      </c>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8">
-        <v>65</v>
-      </c>
-      <c r="V13" s="8">
-        <v>85</v>
-      </c>
-      <c r="W13" s="8">
-        <v>100</v>
-      </c>
-      <c r="X13" s="8">
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>50.2301</v>
+      </c>
+      <c r="S13" s="6">
+        <v>63.150799999999997</v>
+      </c>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6">
+        <v>49.16</v>
+      </c>
+      <c r="V13" s="6">
+        <v>87.29</v>
+      </c>
+      <c r="W13" s="6">
+        <v>100</v>
+      </c>
+      <c r="X13" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D14" s="10">
+        <v>2.5</v>
       </c>
       <c r="E14" s="10">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F14" s="10">
         <v>4.5</v>
       </c>
-      <c r="G14" s="10">
-        <v>4.5</v>
+      <c r="G14" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="H14" s="10">
         <v>3.5</v>
       </c>
-      <c r="I14" s="10">
-        <v>3.5</v>
+      <c r="I14" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="J14" s="13">
         <v>4.5</v>
       </c>
-      <c r="K14" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>64</v>
+      <c r="K14" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L14" s="13">
+        <v>4.5</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>64</v>
+      <c r="N14" s="13">
+        <v>3.5</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>0</v>
-      </c>
-      <c r="R14" s="12">
-        <v>44.628399999999999</v>
-      </c>
-      <c r="S14" s="12">
-        <v>56.1081</v>
-      </c>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12">
-        <v>39.03</v>
-      </c>
-      <c r="V14" s="12">
-        <v>84.757499999999993</v>
-      </c>
-      <c r="W14" s="12">
-        <v>100</v>
-      </c>
-      <c r="X14" s="12">
+        <v>65</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>52.380499999999998</v>
+      </c>
+      <c r="S14" s="6">
+        <v>65.854299999999995</v>
+      </c>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6">
+        <v>31.45</v>
+      </c>
+      <c r="V14" s="6">
+        <v>82.862499999999997</v>
+      </c>
+      <c r="W14" s="6">
+        <v>100</v>
+      </c>
+      <c r="X14" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>34</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="10">
+        <v>3.5</v>
       </c>
       <c r="E15" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="F15" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="G15" s="10">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="H15" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>12</v>
+        <v>3.5</v>
+      </c>
+      <c r="I15" s="10">
+        <v>3.5</v>
       </c>
       <c r="J15" s="13">
         <v>4.5</v>
@@ -1779,14 +1798,14 @@
       <c r="L15" s="13">
         <v>4.5</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>64</v>
+      <c r="M15" s="13">
+        <v>4.5</v>
       </c>
       <c r="N15" s="13">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O15" s="13">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P15" s="13">
         <v>3.5</v>
@@ -1795,17 +1814,17 @@
         <v>0</v>
       </c>
       <c r="R15" s="6">
-        <v>26.4437</v>
+        <v>44.933100000000003</v>
       </c>
       <c r="S15" s="6">
-        <v>33.245800000000003</v>
+        <v>56.491199999999999</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="6">
-        <v>65.08</v>
+        <v>84.7</v>
       </c>
       <c r="V15" s="6">
-        <v>91.27</v>
+        <v>96.174999999999997</v>
       </c>
       <c r="W15" s="6">
         <v>100</v>
@@ -1816,31 +1835,31 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" s="10">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E16" s="10">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F16" s="10">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G16" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>11</v>
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="10">
+        <v>4.5</v>
       </c>
       <c r="I16" s="10">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J16" s="13">
         <v>4.5</v>
@@ -1863,26 +1882,26 @@
       <c r="P16" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="Q16" s="4">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>53</v>
-      </c>
-      <c r="S16" s="6">
-        <v>67</v>
-      </c>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6">
-        <v>45</v>
-      </c>
-      <c r="V16" s="6">
-        <v>84</v>
-      </c>
-      <c r="W16" s="6">
-        <v>100</v>
-      </c>
-      <c r="X16" s="6">
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8">
+        <v>25</v>
+      </c>
+      <c r="S16" s="8">
+        <v>54</v>
+      </c>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8">
+        <v>65</v>
+      </c>
+      <c r="V16" s="8">
+        <v>85</v>
+      </c>
+      <c r="W16" s="8">
+        <v>100</v>
+      </c>
+      <c r="X16" s="8">
         <v>100</v>
       </c>
     </row>
@@ -1891,16 +1910,16 @@
         <v>6</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="D17" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>12</v>
+        <v>36</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="10">
+        <v>3.5</v>
       </c>
       <c r="F17" s="10">
         <v>4.5</v>
@@ -1908,26 +1927,26 @@
       <c r="G17" s="10">
         <v>4.5</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>11</v>
+      <c r="H17" s="10">
+        <v>3.5</v>
       </c>
       <c r="I17" s="10">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J17" s="13">
         <v>4.5</v>
       </c>
-      <c r="K17" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L17" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="M17" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N17" s="13">
-        <v>4.5</v>
+      <c r="K17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="O17" s="13" t="s">
         <v>64</v>
@@ -1935,26 +1954,26 @@
       <c r="P17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="Q17" s="4">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>48.580599999999997</v>
-      </c>
-      <c r="S17" s="6">
-        <v>61.076900000000002</v>
-      </c>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6">
-        <v>83.65</v>
-      </c>
-      <c r="V17" s="6">
-        <v>95.912499999999994</v>
-      </c>
-      <c r="W17" s="6">
-        <v>100</v>
-      </c>
-      <c r="X17" s="6">
+      <c r="Q17" s="11">
+        <v>0</v>
+      </c>
+      <c r="R17" s="12">
+        <v>44.628399999999999</v>
+      </c>
+      <c r="S17" s="12">
+        <v>56.1081</v>
+      </c>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12">
+        <v>39.03</v>
+      </c>
+      <c r="V17" s="12">
+        <v>84.757499999999993</v>
+      </c>
+      <c r="W17" s="12">
+        <v>100</v>
+      </c>
+      <c r="X17" s="12">
         <v>100</v>
       </c>
     </row>
@@ -1963,16 +1982,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>11</v>
+        <v>37</v>
+      </c>
+      <c r="C18" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="10">
+        <v>3.5</v>
       </c>
       <c r="F18" s="10">
         <v>4.5</v>
@@ -1980,48 +1999,48 @@
       <c r="G18" s="10">
         <v>4.5</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>11</v>
+      <c r="H18" s="10">
+        <v>4.5</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J18" s="13">
         <v>4.5</v>
       </c>
-      <c r="K18" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="M18" s="13">
-        <v>3.5</v>
+      <c r="K18" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L18" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="N18" s="13">
         <v>3.5</v>
       </c>
-      <c r="O18" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="P18" s="13" t="s">
-        <v>65</v>
+      <c r="O18" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="P18" s="13">
+        <v>3.5</v>
       </c>
       <c r="Q18" s="4">
         <v>0</v>
       </c>
       <c r="R18" s="6">
-        <v>35.300699999999999</v>
+        <v>26.4437</v>
       </c>
       <c r="S18" s="6">
-        <v>44.381100000000004</v>
+        <v>33.245800000000003</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6">
-        <v>39.450000000000003</v>
+        <v>65.08</v>
       </c>
       <c r="V18" s="6">
-        <v>84.862499999999997</v>
+        <v>91.27</v>
       </c>
       <c r="W18" s="6">
         <v>100</v>
@@ -2035,65 +2054,65 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="D19" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="E19" s="10">
+        <v>2.5</v>
       </c>
       <c r="F19" s="10">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G19" s="10">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I19" s="10">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J19" s="13">
         <v>4.5</v>
       </c>
-      <c r="K19" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>64</v>
+      <c r="K19" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L19" s="13">
+        <v>4.5</v>
       </c>
       <c r="M19" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="N19" s="13">
-        <v>3.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="P19" s="13">
-        <v>2.5</v>
+        <v>64</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="Q19" s="4">
         <v>0</v>
       </c>
       <c r="R19" s="6">
-        <v>54.305300000000003</v>
+        <v>53</v>
       </c>
       <c r="S19" s="6">
-        <v>68.274299999999997</v>
+        <v>67</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6">
-        <v>53.44</v>
+        <v>45</v>
       </c>
       <c r="V19" s="6">
-        <v>88.36</v>
+        <v>84</v>
       </c>
       <c r="W19" s="6">
         <v>100</v>
@@ -2104,16 +2123,16 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="C20" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="D20" s="10">
+        <v>3.5</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>12</v>
@@ -2127,8 +2146,8 @@
       <c r="H20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>12</v>
+      <c r="I20" s="10">
+        <v>4.5</v>
       </c>
       <c r="J20" s="13">
         <v>4.5</v>
@@ -2136,36 +2155,36 @@
       <c r="K20" s="13">
         <v>4.5</v>
       </c>
-      <c r="L20" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20" s="13">
-        <v>3.5</v>
+      <c r="L20" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M20" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N20" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q20" s="4">
         <v>0</v>
       </c>
       <c r="R20" s="6">
-        <v>45.353900000000003</v>
+        <v>48.580599999999997</v>
       </c>
       <c r="S20" s="6">
-        <v>57.020299999999999</v>
+        <v>61.076900000000002</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6">
-        <v>67.77</v>
+        <v>83.65</v>
       </c>
       <c r="V20" s="6">
-        <v>91.942499999999995</v>
+        <v>95.912499999999994</v>
       </c>
       <c r="W20" s="6">
         <v>100</v>
@@ -2176,19 +2195,19 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D21" s="10">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="10">
         <v>4.5</v>
@@ -2199,45 +2218,45 @@
       <c r="H21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="10">
-        <v>3.5</v>
+      <c r="I21" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="J21" s="13">
         <v>4.5</v>
       </c>
-      <c r="K21" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L21" s="13">
-        <v>4.5</v>
+      <c r="K21" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="M21" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O21" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="P21" s="13">
-        <v>3.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N21" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="Q21" s="4">
         <v>0</v>
       </c>
       <c r="R21" s="6">
-        <v>39.660499999999999</v>
+        <v>35.300699999999999</v>
       </c>
       <c r="S21" s="6">
-        <v>49.862299999999998</v>
+        <v>44.381100000000004</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6">
-        <v>51.41</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="V21" s="6">
-        <v>87.852500000000006</v>
+        <v>84.862499999999997</v>
       </c>
       <c r="W21" s="6">
         <v>100</v>
@@ -2248,31 +2267,31 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="D22" s="10">
-        <v>4.5</v>
+        <v>41</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="10">
         <v>4.5</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>11</v>
+      <c r="G22" s="10">
+        <v>4.5</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="I22" s="10">
+        <v>2.5</v>
       </c>
       <c r="J22" s="13">
         <v>4.5</v>
@@ -2286,30 +2305,30 @@
       <c r="M22" s="13">
         <v>3.5</v>
       </c>
-      <c r="N22" s="13" t="s">
+      <c r="N22" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="O22" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="O22" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>66</v>
+      <c r="P22" s="13">
+        <v>2.5</v>
       </c>
       <c r="Q22" s="4">
         <v>0</v>
       </c>
       <c r="R22" s="6">
-        <v>51.510399999999997</v>
+        <v>54.305300000000003</v>
       </c>
       <c r="S22" s="6">
-        <v>64.760300000000001</v>
+        <v>68.274299999999997</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
-        <v>55.77</v>
+        <v>53.44</v>
       </c>
       <c r="V22" s="6">
-        <v>88.942499999999995</v>
+        <v>88.36</v>
       </c>
       <c r="W22" s="6">
         <v>100</v>
@@ -2320,19 +2339,19 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="D23" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="E23" s="10">
-        <v>2.5</v>
+        <v>42</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="F23" s="10">
         <v>4.5</v>
@@ -2343,45 +2362,45 @@
       <c r="H23" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I23" s="10">
-        <v>2.5</v>
+      <c r="I23" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="J23" s="13">
         <v>4.5</v>
       </c>
-      <c r="K23" s="13" t="s">
-        <v>64</v>
+      <c r="K23" s="13">
+        <v>4.5</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="M23" s="13">
-        <v>3.5</v>
+      <c r="M23" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="N23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="P23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="O23" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="P23" s="13" t="s">
-        <v>66</v>
-      </c>
       <c r="Q23" s="4">
         <v>0</v>
       </c>
       <c r="R23" s="6">
-        <v>33.6432</v>
+        <v>45.353900000000003</v>
       </c>
       <c r="S23" s="6">
-        <v>42.297199999999997</v>
+        <v>57.020299999999999</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6">
-        <v>61.37</v>
+        <v>67.77</v>
       </c>
       <c r="V23" s="6">
-        <v>90.342500000000001</v>
+        <v>91.942499999999995</v>
       </c>
       <c r="W23" s="6">
         <v>100</v>
@@ -2392,19 +2411,19 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>11</v>
+        <v>11</v>
+      </c>
+      <c r="D24" s="10">
+        <v>3.5</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" s="10">
         <v>4.5</v>
@@ -2412,11 +2431,11 @@
       <c r="G24" s="10">
         <v>4.5</v>
       </c>
-      <c r="H24" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>11</v>
+      <c r="H24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="10">
+        <v>3.5</v>
       </c>
       <c r="J24" s="13">
         <v>4.5</v>
@@ -2430,30 +2449,30 @@
       <c r="M24" s="13">
         <v>4.5</v>
       </c>
-      <c r="N24" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>64</v>
+      <c r="N24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O24" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="P24" s="13">
+        <v>3.5</v>
       </c>
       <c r="Q24" s="4">
         <v>0</v>
       </c>
       <c r="R24" s="6">
-        <v>25.992799999999999</v>
+        <v>39.660499999999999</v>
       </c>
       <c r="S24" s="6">
-        <v>32.678899999999999</v>
+        <v>49.862299999999998</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6">
-        <v>39.1</v>
+        <v>51.41</v>
       </c>
       <c r="V24" s="6">
-        <v>84.775000000000006</v>
+        <v>87.852500000000006</v>
       </c>
       <c r="W24" s="6">
         <v>100</v>
@@ -2464,19 +2483,19 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C25" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>12</v>
+        <v>6.5</v>
+      </c>
+      <c r="D25" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="E25" s="10">
+        <v>4.5</v>
       </c>
       <c r="F25" s="10">
         <v>4.5</v>
@@ -2484,62 +2503,62 @@
       <c r="G25" s="10">
         <v>4.5</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>12</v>
+      <c r="H25" s="10">
+        <v>3.5</v>
       </c>
       <c r="I25" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K25" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="L25" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="M25" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="N25" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="O25" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="P25" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="Q25" s="7">
-        <v>0</v>
-      </c>
-      <c r="R25" s="8">
-        <v>25.0868</v>
-      </c>
-      <c r="S25" s="8">
-        <v>33.0764</v>
-      </c>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8">
-        <v>48.55</v>
-      </c>
-      <c r="V25" s="8">
-        <v>90.15</v>
-      </c>
-      <c r="W25" s="8">
-        <v>100</v>
-      </c>
-      <c r="X25" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="J25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="K25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="O25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="P25" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>63.9358</v>
+      </c>
+      <c r="S25" s="6">
+        <v>80.382000000000005</v>
+      </c>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6">
+        <v>57.77</v>
+      </c>
+      <c r="V25" s="6">
+        <v>89.442499999999995</v>
+      </c>
+      <c r="W25" s="6">
+        <v>100</v>
+      </c>
+      <c r="X25" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C26" s="9">
         <v>6.5</v>
@@ -2553,51 +2572,51 @@
       <c r="F26" s="10">
         <v>4.5</v>
       </c>
-      <c r="G26" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="H26" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I26" s="10">
-        <v>2.5</v>
+      <c r="G26" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="J26" s="13">
         <v>4.5</v>
       </c>
-      <c r="K26" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L26" s="13">
-        <v>4.5</v>
+      <c r="K26" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="M26" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N26" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="O26" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="P26" s="13">
-        <v>3.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="Q26" s="4">
         <v>0</v>
       </c>
       <c r="R26" s="6">
-        <v>24.203299999999999</v>
+        <v>51.510399999999997</v>
       </c>
       <c r="S26" s="6">
-        <v>30.428999999999998</v>
+        <v>64.760300000000001</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6">
-        <v>32</v>
+        <v>55.77</v>
       </c>
       <c r="V26" s="6">
-        <v>83</v>
+        <v>88.942499999999995</v>
       </c>
       <c r="W26" s="6">
         <v>100</v>
@@ -2611,13 +2630,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C27" s="9">
-        <v>5.5</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>12</v>
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="10">
+        <v>3.5</v>
       </c>
       <c r="E27" s="10">
         <v>2.5</v>
@@ -2628,48 +2647,48 @@
       <c r="G27" s="10">
         <v>4.5</v>
       </c>
-      <c r="H27" s="10">
-        <v>4.5</v>
+      <c r="H27" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="I27" s="10">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J27" s="13">
         <v>4.5</v>
       </c>
-      <c r="K27" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L27" s="13">
-        <v>4.5</v>
+      <c r="K27" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="M27" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N27" s="13">
-        <v>4.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="O27" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="P27" s="13">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="Q27" s="4">
         <v>0</v>
       </c>
       <c r="R27" s="6">
-        <v>25.194400000000002</v>
+        <v>33.6432</v>
       </c>
       <c r="S27" s="6">
-        <v>31.6751</v>
+        <v>42.297199999999997</v>
       </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6">
-        <v>29.07</v>
+        <v>61.37</v>
       </c>
       <c r="V27" s="6">
-        <v>82.267499999999998</v>
+        <v>90.342500000000001</v>
       </c>
       <c r="W27" s="6">
         <v>100</v>
@@ -2683,16 +2702,16 @@
         <v>8</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="10">
-        <v>3.5</v>
+        <v>16</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="10">
         <v>4.5</v>
@@ -2718,8 +2737,8 @@
       <c r="M28" s="13">
         <v>4.5</v>
       </c>
-      <c r="N28" s="13" t="s">
-        <v>64</v>
+      <c r="N28" s="13">
+        <v>4.5</v>
       </c>
       <c r="O28" s="13" t="s">
         <v>64</v>
@@ -2731,17 +2750,17 @@
         <v>0</v>
       </c>
       <c r="R28" s="6">
-        <v>35.718299999999999</v>
+        <v>25.992799999999999</v>
       </c>
       <c r="S28" s="6">
-        <v>44.906100000000002</v>
+        <v>32.678899999999999</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6">
-        <v>55.43</v>
+        <v>39.1</v>
       </c>
       <c r="V28" s="6">
-        <v>88.857500000000002</v>
+        <v>84.775000000000006</v>
       </c>
       <c r="W28" s="6">
         <v>100</v>
@@ -2752,19 +2771,19 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="C29" s="9">
+        <v>4.5</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F29" s="10">
         <v>4.5</v>
@@ -2772,48 +2791,48 @@
       <c r="G29" s="10">
         <v>4.5</v>
       </c>
-      <c r="H29" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J29" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="K29" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L29" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="M29" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N29" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O29" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="P29" s="13">
-        <v>3.5</v>
+      <c r="H29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K29" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="L29" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="P29" s="14">
+        <v>1.5</v>
       </c>
       <c r="Q29" s="7">
         <v>0</v>
       </c>
       <c r="R29" s="8">
-        <v>20</v>
+        <v>25.0868</v>
       </c>
       <c r="S29" s="8">
-        <v>27</v>
+        <v>33.0764</v>
       </c>
       <c r="T29" s="8"/>
       <c r="U29" s="8">
-        <v>51.14</v>
+        <v>48.55</v>
       </c>
       <c r="V29" s="8">
-        <v>93.95</v>
+        <v>90.15</v>
       </c>
       <c r="W29" s="8">
         <v>100</v>
@@ -2824,56 +2843,344 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="D30" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G30" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="I30" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="J30" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L30" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M30" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N30" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="O30" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="P30" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>24.203299999999999</v>
+      </c>
+      <c r="S30" s="6">
+        <v>30.428999999999998</v>
+      </c>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6">
+        <v>32</v>
+      </c>
+      <c r="V30" s="6">
+        <v>83</v>
+      </c>
+      <c r="W30" s="6">
+        <v>100</v>
+      </c>
+      <c r="X30" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F31" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G31" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="I31" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="K31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="O31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="P31" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <v>25.194400000000002</v>
+      </c>
+      <c r="S31" s="6">
+        <v>31.6751</v>
+      </c>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6">
+        <v>29.07</v>
+      </c>
+      <c r="V31" s="6">
+        <v>82.267499999999998</v>
+      </c>
+      <c r="W31" s="6">
+        <v>100</v>
+      </c>
+      <c r="X31" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G32" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="H32" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="K32" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L32" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M32" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0</v>
+      </c>
+      <c r="R32" s="6">
+        <v>35.718299999999999</v>
+      </c>
+      <c r="S32" s="6">
+        <v>44.906100000000002</v>
+      </c>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6">
+        <v>55.43</v>
+      </c>
+      <c r="V32" s="6">
+        <v>88.857500000000002</v>
+      </c>
+      <c r="W32" s="6">
+        <v>100</v>
+      </c>
+      <c r="X32" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="H33" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="K33" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M33" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O33" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="P33" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8">
+        <v>20</v>
+      </c>
+      <c r="S33" s="8">
+        <v>27</v>
+      </c>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8">
+        <v>51.14</v>
+      </c>
+      <c r="V33" s="8">
+        <v>93.95</v>
+      </c>
+      <c r="W33" s="8">
+        <v>100</v>
+      </c>
+      <c r="X33" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C34" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="G30" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="H30" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J30" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="K30" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="L30" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="M30" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="N30" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="O30" s="13">
-        <v>3.5</v>
-      </c>
-      <c r="P30" s="13">
+      <c r="D34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="G34" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="H34" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="K34" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="L34" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="M34" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="O34" s="13">
+        <v>3.5</v>
+      </c>
+      <c r="P34" s="13">
         <v>3.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X30" xr:uid="{25ACC554-19B0-43F2-ABD1-883041E60297}"/>
+  <autoFilter ref="A1:X34" xr:uid="{25ACC554-19B0-43F2-ABD1-883041E60297}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
